--- a/assets/確認事項一覧_テンプレート.xlsx
+++ b/assets/確認事項一覧_テンプレート.xlsx
@@ -19,14 +19,13 @@
   <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Yu Gothic UI"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Yu Gothic UI"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
